--- a/Team-Data/2008-09/4-10-2008-09.xlsx
+++ b/Team-Data/2008-09/4-10-2008-09.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,28 +728,28 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E2" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F2" t="n">
         <v>34</v>
       </c>
       <c r="G2" t="n">
-        <v>0.575</v>
+        <v>0.57</v>
       </c>
       <c r="H2" t="n">
         <v>48.1</v>
       </c>
       <c r="I2" t="n">
-        <v>36.2</v>
+        <v>36.1</v>
       </c>
       <c r="J2" t="n">
         <v>78.8</v>
       </c>
       <c r="K2" t="n">
-        <v>0.459</v>
+        <v>0.458</v>
       </c>
       <c r="L2" t="n">
         <v>7.3</v>
@@ -691,13 +758,13 @@
         <v>20.1</v>
       </c>
       <c r="N2" t="n">
-        <v>0.366</v>
+        <v>0.365</v>
       </c>
       <c r="O2" t="n">
-        <v>18.8</v>
+        <v>18.6</v>
       </c>
       <c r="P2" t="n">
-        <v>25.4</v>
+        <v>25.2</v>
       </c>
       <c r="Q2" t="n">
         <v>0.738</v>
@@ -727,19 +794,19 @@
         <v>4.2</v>
       </c>
       <c r="Z2" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>98.40000000000001</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="AC2" t="n">
         <v>1.7</v>
       </c>
       <c r="AD2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE2" t="n">
         <v>12</v>
@@ -760,7 +827,7 @@
         <v>24</v>
       </c>
       <c r="AK2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AL2" t="n">
         <v>8</v>
@@ -769,16 +836,16 @@
         <v>7</v>
       </c>
       <c r="AN2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AO2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AP2" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AQ2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AR2" t="n">
         <v>20</v>
@@ -790,13 +857,13 @@
         <v>22</v>
       </c>
       <c r="AU2" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AV2" t="n">
         <v>6</v>
       </c>
       <c r="AW2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AX2" t="n">
         <v>19</v>
@@ -808,13 +875,13 @@
         <v>4</v>
       </c>
       <c r="BA2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BB2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BC2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>4-10-2008-09</t>
+          <t>2009-04-10</t>
         </is>
       </c>
     </row>
@@ -861,28 +928,28 @@
         <v>37.5</v>
       </c>
       <c r="J3" t="n">
-        <v>77.09999999999999</v>
+        <v>77</v>
       </c>
       <c r="K3" t="n">
-        <v>0.487</v>
+        <v>0.486</v>
       </c>
       <c r="L3" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="M3" t="n">
         <v>16.5</v>
       </c>
       <c r="N3" t="n">
-        <v>0.396</v>
+        <v>0.392</v>
       </c>
       <c r="O3" t="n">
         <v>19.6</v>
       </c>
       <c r="P3" t="n">
-        <v>25.4</v>
+        <v>25.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.773</v>
+        <v>0.768</v>
       </c>
       <c r="R3" t="n">
         <v>10.6</v>
@@ -891,7 +958,7 @@
         <v>31.8</v>
       </c>
       <c r="T3" t="n">
-        <v>42.4</v>
+        <v>42.3</v>
       </c>
       <c r="U3" t="n">
         <v>22.7</v>
@@ -900,28 +967,28 @@
         <v>15.7</v>
       </c>
       <c r="W3" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="X3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Y3" t="n">
         <v>4.7</v>
       </c>
       <c r="Z3" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="AA3" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="AB3" t="n">
-        <v>101.2</v>
+        <v>101</v>
       </c>
       <c r="AC3" t="n">
         <v>8.1</v>
       </c>
       <c r="AD3" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="AE3" t="n">
         <v>3</v>
@@ -948,7 +1015,7 @@
         <v>20</v>
       </c>
       <c r="AM3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AN3" t="n">
         <v>1</v>
@@ -957,10 +1024,10 @@
         <v>12</v>
       </c>
       <c r="AP3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AQ3" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AR3" t="n">
         <v>21</v>
@@ -975,7 +1042,7 @@
         <v>4</v>
       </c>
       <c r="AV3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AW3" t="n">
         <v>7</v>
@@ -990,10 +1057,10 @@
         <v>27</v>
       </c>
       <c r="BA3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BB3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BC3" t="n">
         <v>2</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>4-10-2008-09</t>
+          <t>2009-04-10</t>
         </is>
       </c>
     </row>
@@ -1025,43 +1092,43 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E4" t="n">
         <v>35</v>
       </c>
       <c r="F4" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G4" t="n">
-        <v>0.443</v>
+        <v>0.449</v>
       </c>
       <c r="H4" t="n">
         <v>48.6</v>
       </c>
       <c r="I4" t="n">
-        <v>35.1</v>
+        <v>35.2</v>
       </c>
       <c r="J4" t="n">
-        <v>77</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>0.456</v>
+        <v>0.457</v>
       </c>
       <c r="L4" t="n">
         <v>6.1</v>
       </c>
       <c r="M4" t="n">
-        <v>16.5</v>
+        <v>16.4</v>
       </c>
       <c r="N4" t="n">
-        <v>0.367</v>
+        <v>0.369</v>
       </c>
       <c r="O4" t="n">
         <v>17.6</v>
       </c>
       <c r="P4" t="n">
-        <v>23.7</v>
+        <v>23.8</v>
       </c>
       <c r="Q4" t="n">
         <v>0.742</v>
@@ -1076,13 +1143,13 @@
         <v>39.7</v>
       </c>
       <c r="U4" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="V4" t="n">
-        <v>15.6</v>
+        <v>15.7</v>
       </c>
       <c r="W4" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="X4" t="n">
         <v>4.8</v>
@@ -1091,19 +1158,19 @@
         <v>5.9</v>
       </c>
       <c r="Z4" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="AB4" t="n">
-        <v>93.8</v>
+        <v>94</v>
       </c>
       <c r="AC4" t="n">
-        <v>-0.9</v>
+        <v>-0.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE4" t="n">
         <v>18</v>
@@ -1115,7 +1182,7 @@
         <v>18</v>
       </c>
       <c r="AH4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI4" t="n">
         <v>29</v>
@@ -1124,13 +1191,13 @@
         <v>30</v>
       </c>
       <c r="AK4" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AL4" t="n">
         <v>22</v>
       </c>
       <c r="AM4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AN4" t="n">
         <v>14</v>
@@ -1148,7 +1215,7 @@
         <v>17</v>
       </c>
       <c r="AS4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AT4" t="n">
         <v>27</v>
@@ -1175,7 +1242,7 @@
         <v>13</v>
       </c>
       <c r="BB4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BC4" t="n">
         <v>18</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>4-10-2008-09</t>
+          <t>2009-04-10</t>
         </is>
       </c>
     </row>
@@ -1207,28 +1274,28 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E5" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F5" t="n">
         <v>40</v>
       </c>
       <c r="G5" t="n">
-        <v>0.487</v>
+        <v>0.494</v>
       </c>
       <c r="H5" t="n">
         <v>48.6</v>
       </c>
       <c r="I5" t="n">
-        <v>38.2</v>
+        <v>38.1</v>
       </c>
       <c r="J5" t="n">
-        <v>83.59999999999999</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>0.456</v>
+        <v>0.457</v>
       </c>
       <c r="L5" t="n">
         <v>6</v>
@@ -1237,31 +1304,31 @@
         <v>15.7</v>
       </c>
       <c r="N5" t="n">
-        <v>0.382</v>
+        <v>0.383</v>
       </c>
       <c r="O5" t="n">
-        <v>19.8</v>
+        <v>20</v>
       </c>
       <c r="P5" t="n">
-        <v>24.9</v>
+        <v>25.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.797</v>
+        <v>0.796</v>
       </c>
       <c r="R5" t="n">
         <v>11.9</v>
       </c>
       <c r="S5" t="n">
-        <v>30.4</v>
+        <v>30.3</v>
       </c>
       <c r="T5" t="n">
-        <v>42.3</v>
+        <v>42.2</v>
       </c>
       <c r="U5" t="n">
         <v>21</v>
       </c>
       <c r="V5" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="W5" t="n">
         <v>7.5</v>
@@ -1270,34 +1337,34 @@
         <v>5.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="Z5" t="n">
         <v>20.9</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="AB5" t="n">
         <v>102.2</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.4</v>
+        <v>-0.3</v>
       </c>
       <c r="AD5" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="AE5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AF5" t="n">
         <v>16</v>
       </c>
       <c r="AG5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AH5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AI5" t="n">
         <v>8</v>
@@ -1306,7 +1373,7 @@
         <v>5</v>
       </c>
       <c r="AK5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AL5" t="n">
         <v>23</v>
@@ -1315,10 +1382,10 @@
         <v>24</v>
       </c>
       <c r="AN5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AO5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AP5" t="n">
         <v>14</v>
@@ -1336,10 +1403,10 @@
         <v>8</v>
       </c>
       <c r="AU5" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AV5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW5" t="n">
         <v>9</v>
@@ -1360,7 +1427,7 @@
         <v>8</v>
       </c>
       <c r="BC5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>4-10-2008-09</t>
+          <t>2009-04-10</t>
         </is>
       </c>
     </row>
@@ -1392,58 +1459,58 @@
         <v>78</v>
       </c>
       <c r="E6" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G6" t="n">
-        <v>0.821</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="H6" t="n">
         <v>48.2</v>
       </c>
       <c r="I6" t="n">
-        <v>36.8</v>
+        <v>36.7</v>
       </c>
       <c r="J6" t="n">
-        <v>78.7</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="K6" t="n">
         <v>0.467</v>
       </c>
       <c r="L6" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="M6" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="N6" t="n">
-        <v>0.392</v>
+        <v>0.388</v>
       </c>
       <c r="O6" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="P6" t="n">
-        <v>24.4</v>
+        <v>24.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.757</v>
+        <v>0.756</v>
       </c>
       <c r="R6" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="S6" t="n">
-        <v>31.3</v>
+        <v>31.5</v>
       </c>
       <c r="T6" t="n">
-        <v>42.1</v>
+        <v>42.2</v>
       </c>
       <c r="U6" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="V6" t="n">
-        <v>12.5</v>
+        <v>12.7</v>
       </c>
       <c r="W6" t="n">
         <v>7.3</v>
@@ -1452,22 +1519,22 @@
         <v>5.3</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Z6" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="AA6" t="n">
-        <v>20.1</v>
+        <v>20.3</v>
       </c>
       <c r="AB6" t="n">
-        <v>100.1</v>
+        <v>99.8</v>
       </c>
       <c r="AC6" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD6" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="AE6" t="n">
         <v>1</v>
@@ -1491,7 +1558,7 @@
         <v>6</v>
       </c>
       <c r="AL6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM6" t="n">
         <v>5</v>
@@ -1500,13 +1567,13 @@
         <v>2</v>
       </c>
       <c r="AO6" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AP6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ6" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AR6" t="n">
         <v>19</v>
@@ -1515,28 +1582,28 @@
         <v>8</v>
       </c>
       <c r="AT6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AU6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AV6" t="n">
         <v>4</v>
       </c>
       <c r="AW6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AX6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY6" t="n">
         <v>4</v>
       </c>
       <c r="AZ6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BB6" t="n">
         <v>13</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>4-10-2008-09</t>
+          <t>2009-04-10</t>
         </is>
       </c>
     </row>
@@ -1571,16 +1638,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E7" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F7" t="n">
         <v>31</v>
       </c>
       <c r="G7" t="n">
-        <v>0.608</v>
+        <v>0.603</v>
       </c>
       <c r="H7" t="n">
         <v>48.3</v>
@@ -1592,40 +1659,40 @@
         <v>82.7</v>
       </c>
       <c r="K7" t="n">
-        <v>0.462</v>
+        <v>0.463</v>
       </c>
       <c r="L7" t="n">
         <v>7</v>
       </c>
       <c r="M7" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="N7" t="n">
-        <v>0.349</v>
+        <v>0.352</v>
       </c>
       <c r="O7" t="n">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="P7" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="Q7" t="n">
         <v>0.8169999999999999</v>
       </c>
       <c r="R7" t="n">
-        <v>11.2</v>
+        <v>11.1</v>
       </c>
       <c r="S7" t="n">
         <v>31.6</v>
       </c>
       <c r="T7" t="n">
-        <v>42.8</v>
+        <v>42.7</v>
       </c>
       <c r="U7" t="n">
         <v>21.7</v>
       </c>
       <c r="V7" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="W7" t="n">
         <v>7.3</v>
@@ -1643,22 +1710,22 @@
         <v>20</v>
       </c>
       <c r="AB7" t="n">
-        <v>102</v>
+        <v>102.1</v>
       </c>
       <c r="AC7" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AD7" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AH7" t="n">
         <v>14</v>
@@ -1679,13 +1746,13 @@
         <v>8</v>
       </c>
       <c r="AN7" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AO7" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AP7" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AQ7" t="n">
         <v>2</v>
@@ -1694,22 +1761,22 @@
         <v>13</v>
       </c>
       <c r="AS7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AT7" t="n">
         <v>5</v>
       </c>
       <c r="AU7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AV7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AX7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AY7" t="n">
         <v>7</v>
@@ -1718,13 +1785,13 @@
         <v>5</v>
       </c>
       <c r="BA7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BB7" t="n">
         <v>9</v>
       </c>
       <c r="BC7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BD7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>4-10-2008-09</t>
+          <t>2009-04-10</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1922,7 @@
         <v>5</v>
       </c>
       <c r="AL8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AM8" t="n">
         <v>18</v>
@@ -1864,7 +1931,7 @@
         <v>13</v>
       </c>
       <c r="AO8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AP8" t="n">
         <v>1</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>4-10-2008-09</t>
+          <t>2009-04-10</t>
         </is>
       </c>
     </row>
@@ -1935,16 +2002,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E9" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F9" t="n">
         <v>40</v>
       </c>
       <c r="G9" t="n">
-        <v>0.494</v>
+        <v>0.487</v>
       </c>
       <c r="H9" t="n">
         <v>48.5</v>
@@ -1953,10 +2020,10 @@
         <v>36.4</v>
       </c>
       <c r="J9" t="n">
-        <v>79.90000000000001</v>
+        <v>80</v>
       </c>
       <c r="K9" t="n">
-        <v>0.455</v>
+        <v>0.454</v>
       </c>
       <c r="L9" t="n">
         <v>4.6</v>
@@ -1971,13 +2038,13 @@
         <v>16.8</v>
       </c>
       <c r="P9" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.751</v>
+        <v>0.753</v>
       </c>
       <c r="R9" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="S9" t="n">
         <v>29.8</v>
@@ -1989,7 +2056,7 @@
         <v>20.7</v>
       </c>
       <c r="V9" t="n">
-        <v>11.9</v>
+        <v>12</v>
       </c>
       <c r="W9" t="n">
         <v>6.1</v>
@@ -2001,31 +2068,31 @@
         <v>4.1</v>
       </c>
       <c r="Z9" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="AA9" t="n">
         <v>19.6</v>
       </c>
       <c r="AB9" t="n">
-        <v>94.2</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="AC9" t="n">
-        <v>-0.3</v>
+        <v>-0.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AF9" t="n">
         <v>16</v>
       </c>
       <c r="AG9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AH9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI9" t="n">
         <v>22</v>
@@ -2043,10 +2110,10 @@
         <v>28</v>
       </c>
       <c r="AN9" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AO9" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AP9" t="n">
         <v>29</v>
@@ -2058,7 +2125,7 @@
         <v>10</v>
       </c>
       <c r="AS9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AT9" t="n">
         <v>16</v>
@@ -2076,7 +2143,7 @@
         <v>18</v>
       </c>
       <c r="AY9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ9" t="n">
         <v>19</v>
@@ -2088,7 +2155,7 @@
         <v>28</v>
       </c>
       <c r="BC9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>4-10-2008-09</t>
+          <t>2009-04-10</t>
         </is>
       </c>
     </row>
@@ -2117,16 +2184,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E10" t="n">
         <v>28</v>
       </c>
       <c r="F10" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G10" t="n">
-        <v>0.354</v>
+        <v>0.359</v>
       </c>
       <c r="H10" t="n">
         <v>48.5</v>
@@ -2138,7 +2205,7 @@
         <v>86.2</v>
       </c>
       <c r="K10" t="n">
-        <v>0.458</v>
+        <v>0.459</v>
       </c>
       <c r="L10" t="n">
         <v>6.8</v>
@@ -2147,37 +2214,37 @@
         <v>18.1</v>
       </c>
       <c r="N10" t="n">
-        <v>0.374</v>
+        <v>0.373</v>
       </c>
       <c r="O10" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="P10" t="n">
-        <v>29.2</v>
+        <v>29.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.792</v>
+        <v>0.791</v>
       </c>
       <c r="R10" t="n">
         <v>11.6</v>
       </c>
       <c r="S10" t="n">
-        <v>30.3</v>
+        <v>30.5</v>
       </c>
       <c r="T10" t="n">
-        <v>41.9</v>
+        <v>42.1</v>
       </c>
       <c r="U10" t="n">
         <v>21</v>
       </c>
       <c r="V10" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="W10" t="n">
         <v>7.9</v>
       </c>
       <c r="X10" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="Y10" t="n">
         <v>5.1</v>
@@ -2195,7 +2262,7 @@
         <v>-3.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE10" t="n">
         <v>24</v>
@@ -2216,19 +2283,19 @@
         <v>3</v>
       </c>
       <c r="AK10" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AL10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AM10" t="n">
         <v>17</v>
       </c>
       <c r="AN10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AO10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AP10" t="n">
         <v>2</v>
@@ -2240,16 +2307,16 @@
         <v>9</v>
       </c>
       <c r="AS10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU10" t="n">
         <v>15</v>
       </c>
-      <c r="AT10" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>14</v>
-      </c>
       <c r="AV10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW10" t="n">
         <v>6</v>
@@ -2258,7 +2325,7 @@
         <v>1</v>
       </c>
       <c r="AY10" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AZ10" t="n">
         <v>24</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>4-10-2008-09</t>
+          <t>2009-04-10</t>
         </is>
       </c>
     </row>
@@ -2299,61 +2366,61 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E11" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F11" t="n">
         <v>28</v>
       </c>
       <c r="G11" t="n">
-        <v>0.65</v>
+        <v>0.646</v>
       </c>
       <c r="H11" t="n">
         <v>48.3</v>
       </c>
       <c r="I11" t="n">
-        <v>36.2</v>
+        <v>36.1</v>
       </c>
       <c r="J11" t="n">
         <v>79.59999999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>0.454</v>
+        <v>0.453</v>
       </c>
       <c r="L11" t="n">
         <v>7.7</v>
       </c>
       <c r="M11" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="N11" t="n">
         <v>0.378</v>
       </c>
       <c r="O11" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="P11" t="n">
-        <v>23.4</v>
+        <v>23.3</v>
       </c>
       <c r="Q11" t="n">
         <v>0.803</v>
       </c>
       <c r="R11" t="n">
-        <v>10.6</v>
+        <v>10.5</v>
       </c>
       <c r="S11" t="n">
-        <v>32.4</v>
+        <v>32.5</v>
       </c>
       <c r="T11" t="n">
-        <v>43</v>
+        <v>42.9</v>
       </c>
       <c r="U11" t="n">
         <v>20.3</v>
       </c>
       <c r="V11" t="n">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="W11" t="n">
         <v>6.7</v>
@@ -2365,31 +2432,31 @@
         <v>5.4</v>
       </c>
       <c r="Z11" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="AA11" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="AB11" t="n">
-        <v>98.8</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="AC11" t="n">
         <v>4</v>
       </c>
       <c r="AD11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE11" t="n">
         <v>6</v>
       </c>
       <c r="AF11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AH11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI11" t="n">
         <v>24</v>
@@ -2410,7 +2477,7 @@
         <v>8</v>
       </c>
       <c r="AO11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP11" t="n">
         <v>21</v>
@@ -2428,16 +2495,16 @@
         <v>4</v>
       </c>
       <c r="AU11" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AV11" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AW11" t="n">
         <v>25</v>
       </c>
       <c r="AX11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AY11" t="n">
         <v>24</v>
@@ -2446,7 +2513,7 @@
         <v>2</v>
       </c>
       <c r="BA11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BB11" t="n">
         <v>17</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>4-10-2008-09</t>
+          <t>2009-04-10</t>
         </is>
       </c>
     </row>
@@ -2481,28 +2548,28 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E12" t="n">
         <v>34</v>
       </c>
       <c r="F12" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G12" t="n">
-        <v>0.43</v>
+        <v>0.436</v>
       </c>
       <c r="H12" t="n">
         <v>48.4</v>
       </c>
       <c r="I12" t="n">
-        <v>39.3</v>
+        <v>39.2</v>
       </c>
       <c r="J12" t="n">
         <v>86.40000000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>0.455</v>
+        <v>0.454</v>
       </c>
       <c r="L12" t="n">
         <v>7.9</v>
@@ -2511,16 +2578,16 @@
         <v>21</v>
       </c>
       <c r="N12" t="n">
-        <v>0.375</v>
+        <v>0.374</v>
       </c>
       <c r="O12" t="n">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="P12" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.806</v>
       </c>
       <c r="R12" t="n">
         <v>11.2</v>
@@ -2547,19 +2614,19 @@
         <v>5.4</v>
       </c>
       <c r="Z12" t="n">
-        <v>23.3</v>
+        <v>23.2</v>
       </c>
       <c r="AA12" t="n">
         <v>20.7</v>
       </c>
       <c r="AB12" t="n">
-        <v>104.9</v>
+        <v>104.7</v>
       </c>
       <c r="AC12" t="n">
         <v>-1.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE12" t="n">
         <v>19</v>
@@ -2571,7 +2638,7 @@
         <v>19</v>
       </c>
       <c r="AH12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AI12" t="n">
         <v>4</v>
@@ -2592,7 +2659,7 @@
         <v>9</v>
       </c>
       <c r="AO12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AP12" t="n">
         <v>24</v>
@@ -2610,13 +2677,13 @@
         <v>2</v>
       </c>
       <c r="AU12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AW12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX12" t="n">
         <v>9</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>4-10-2008-09</t>
+          <t>2009-04-10</t>
         </is>
       </c>
     </row>
@@ -2663,28 +2730,28 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F13" t="n">
         <v>60</v>
       </c>
       <c r="G13" t="n">
-        <v>0.241</v>
+        <v>0.231</v>
       </c>
       <c r="H13" t="n">
         <v>48.5</v>
       </c>
       <c r="I13" t="n">
-        <v>36.1</v>
+        <v>36</v>
       </c>
       <c r="J13" t="n">
         <v>81.7</v>
       </c>
       <c r="K13" t="n">
-        <v>0.442</v>
+        <v>0.441</v>
       </c>
       <c r="L13" t="n">
         <v>6.6</v>
@@ -2699,22 +2766,22 @@
         <v>16.8</v>
       </c>
       <c r="P13" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.737</v>
+        <v>0.738</v>
       </c>
       <c r="R13" t="n">
         <v>11</v>
       </c>
       <c r="S13" t="n">
-        <v>29</v>
+        <v>28.8</v>
       </c>
       <c r="T13" t="n">
-        <v>40</v>
+        <v>39.8</v>
       </c>
       <c r="U13" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="V13" t="n">
         <v>14.8</v>
@@ -2723,25 +2790,25 @@
         <v>6.9</v>
       </c>
       <c r="X13" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="Y13" t="n">
         <v>5.1</v>
       </c>
       <c r="Z13" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="AA13" t="n">
         <v>19.7</v>
       </c>
       <c r="AB13" t="n">
-        <v>95.7</v>
+        <v>95.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>-8.1</v>
+        <v>-8.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE13" t="n">
         <v>28</v>
@@ -2753,7 +2820,7 @@
         <v>28</v>
       </c>
       <c r="AH13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI13" t="n">
         <v>25</v>
@@ -2762,10 +2829,10 @@
         <v>10</v>
       </c>
       <c r="AK13" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AL13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AM13" t="n">
         <v>16</v>
@@ -2774,31 +2841,31 @@
         <v>21</v>
       </c>
       <c r="AO13" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AP13" t="n">
         <v>25</v>
       </c>
       <c r="AQ13" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AR13" t="n">
         <v>15</v>
       </c>
       <c r="AS13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AT13" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AU13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AV13" t="n">
         <v>22</v>
       </c>
       <c r="AW13" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AX13" t="n">
         <v>3</v>
@@ -2807,7 +2874,7 @@
         <v>18</v>
       </c>
       <c r="AZ13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BA13" t="n">
         <v>27</v>
@@ -2816,7 +2883,7 @@
         <v>27</v>
       </c>
       <c r="BC13" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BD13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>4-10-2008-09</t>
+          <t>2009-04-10</t>
         </is>
       </c>
     </row>
@@ -2848,13 +2915,13 @@
         <v>79</v>
       </c>
       <c r="E14" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G14" t="n">
-        <v>0.785</v>
+        <v>0.797</v>
       </c>
       <c r="H14" t="n">
         <v>48.3</v>
@@ -2863,7 +2930,7 @@
         <v>40.3</v>
       </c>
       <c r="J14" t="n">
-        <v>85.2</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="K14" t="n">
         <v>0.473</v>
@@ -2872,10 +2939,10 @@
         <v>6.7</v>
       </c>
       <c r="M14" t="n">
-        <v>18.7</v>
+        <v>18.6</v>
       </c>
       <c r="N14" t="n">
-        <v>0.358</v>
+        <v>0.36</v>
       </c>
       <c r="O14" t="n">
         <v>19.7</v>
@@ -2884,34 +2951,34 @@
         <v>25.7</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.768</v>
+        <v>0.769</v>
       </c>
       <c r="R14" t="n">
         <v>12.5</v>
       </c>
       <c r="S14" t="n">
-        <v>31.5</v>
+        <v>31.7</v>
       </c>
       <c r="T14" t="n">
-        <v>44</v>
+        <v>44.1</v>
       </c>
       <c r="U14" t="n">
         <v>23.2</v>
       </c>
       <c r="V14" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="W14" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="X14" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Y14" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Z14" t="n">
-        <v>20.6</v>
+        <v>20.4</v>
       </c>
       <c r="AA14" t="n">
         <v>22.2</v>
@@ -2920,13 +2987,13 @@
         <v>107</v>
       </c>
       <c r="AC14" t="n">
-        <v>7.3</v>
+        <v>7.7</v>
       </c>
       <c r="AD14" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AE14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF14" t="n">
         <v>2</v>
@@ -2935,7 +3002,7 @@
         <v>2</v>
       </c>
       <c r="AH14" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI14" t="n">
         <v>2</v>
@@ -2950,10 +3017,10 @@
         <v>16</v>
       </c>
       <c r="AM14" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AN14" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AO14" t="n">
         <v>11</v>
@@ -2962,13 +3029,13 @@
         <v>8</v>
       </c>
       <c r="AQ14" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR14" t="n">
         <v>3</v>
       </c>
       <c r="AS14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AT14" t="n">
         <v>1</v>
@@ -2983,16 +3050,16 @@
         <v>2</v>
       </c>
       <c r="AX14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BA14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BB14" t="n">
         <v>3</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>4-10-2008-09</t>
+          <t>2009-04-10</t>
         </is>
       </c>
     </row>
@@ -3027,67 +3094,67 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F15" t="n">
         <v>56</v>
       </c>
       <c r="G15" t="n">
-        <v>0.291</v>
+        <v>0.282</v>
       </c>
       <c r="H15" t="n">
         <v>48.3</v>
       </c>
       <c r="I15" t="n">
-        <v>35</v>
+        <v>34.9</v>
       </c>
       <c r="J15" t="n">
-        <v>77.09999999999999</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>0.454</v>
+        <v>0.453</v>
       </c>
       <c r="L15" t="n">
         <v>4.8</v>
       </c>
       <c r="M15" t="n">
-        <v>13.5</v>
+        <v>13.4</v>
       </c>
       <c r="N15" t="n">
-        <v>0.359</v>
+        <v>0.358</v>
       </c>
       <c r="O15" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="P15" t="n">
         <v>25.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.756</v>
+        <v>0.757</v>
       </c>
       <c r="R15" t="n">
-        <v>10.5</v>
+        <v>10.4</v>
       </c>
       <c r="S15" t="n">
-        <v>28.4</v>
+        <v>28.3</v>
       </c>
       <c r="T15" t="n">
-        <v>38.8</v>
+        <v>38.7</v>
       </c>
       <c r="U15" t="n">
-        <v>17.3</v>
+        <v>17.2</v>
       </c>
       <c r="V15" t="n">
         <v>15.2</v>
       </c>
       <c r="W15" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="X15" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Y15" t="n">
         <v>5.4</v>
@@ -3096,16 +3163,16 @@
         <v>21.7</v>
       </c>
       <c r="AA15" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="AB15" t="n">
-        <v>93.90000000000001</v>
+        <v>93.7</v>
       </c>
       <c r="AC15" t="n">
-        <v>-5.4</v>
+        <v>-5.7</v>
       </c>
       <c r="AD15" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE15" t="n">
         <v>26</v>
@@ -3129,22 +3196,22 @@
         <v>22</v>
       </c>
       <c r="AL15" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AM15" t="n">
         <v>27</v>
       </c>
       <c r="AN15" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AO15" t="n">
         <v>13</v>
       </c>
       <c r="AP15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AQ15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AR15" t="n">
         <v>23</v>
@@ -3162,10 +3229,10 @@
         <v>24</v>
       </c>
       <c r="AW15" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AX15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY15" t="n">
         <v>26</v>
@@ -3177,7 +3244,7 @@
         <v>9</v>
       </c>
       <c r="BB15" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BC15" t="n">
         <v>26</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>4-10-2008-09</t>
+          <t>2009-04-10</t>
         </is>
       </c>
     </row>
@@ -3209,16 +3276,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E16" t="n">
         <v>41</v>
       </c>
       <c r="F16" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G16" t="n">
-        <v>0.519</v>
+        <v>0.526</v>
       </c>
       <c r="H16" t="n">
         <v>48.6</v>
@@ -3227,7 +3294,7 @@
         <v>36.9</v>
       </c>
       <c r="J16" t="n">
-        <v>81.09999999999999</v>
+        <v>81</v>
       </c>
       <c r="K16" t="n">
         <v>0.456</v>
@@ -3248,7 +3315,7 @@
         <v>23</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.756</v>
+        <v>0.758</v>
       </c>
       <c r="R16" t="n">
         <v>10</v>
@@ -3263,7 +3330,7 @@
         <v>20.4</v>
       </c>
       <c r="V16" t="n">
-        <v>12.4</v>
+        <v>12.5</v>
       </c>
       <c r="W16" t="n">
         <v>8.1</v>
@@ -3284,10 +3351,10 @@
         <v>98.2</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE16" t="n">
         <v>14</v>
@@ -3299,16 +3366,16 @@
         <v>14</v>
       </c>
       <c r="AH16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI16" t="n">
         <v>13</v>
       </c>
       <c r="AJ16" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AK16" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AL16" t="n">
         <v>12</v>
@@ -3326,7 +3393,7 @@
         <v>23</v>
       </c>
       <c r="AQ16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AR16" t="n">
         <v>26</v>
@@ -3356,10 +3423,10 @@
         <v>17</v>
       </c>
       <c r="BA16" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BB16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BC16" t="n">
         <v>15</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>4-10-2008-09</t>
+          <t>2009-04-10</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E17" t="n">
         <v>32</v>
       </c>
       <c r="F17" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G17" t="n">
-        <v>0.41</v>
+        <v>0.405</v>
       </c>
       <c r="H17" t="n">
         <v>48.3</v>
@@ -3412,40 +3479,40 @@
         <v>82.2</v>
       </c>
       <c r="K17" t="n">
-        <v>0.444</v>
+        <v>0.445</v>
       </c>
       <c r="L17" t="n">
         <v>6.2</v>
       </c>
       <c r="M17" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="N17" t="n">
-        <v>0.361</v>
+        <v>0.362</v>
       </c>
       <c r="O17" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="P17" t="n">
-        <v>25.4</v>
+        <v>25.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.781</v>
+        <v>0.78</v>
       </c>
       <c r="R17" t="n">
         <v>11.9</v>
       </c>
       <c r="S17" t="n">
-        <v>28.8</v>
+        <v>28.7</v>
       </c>
       <c r="T17" t="n">
-        <v>40.7</v>
+        <v>40.5</v>
       </c>
       <c r="U17" t="n">
         <v>21.7</v>
       </c>
       <c r="V17" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="W17" t="n">
         <v>7.4</v>
@@ -3460,31 +3527,31 @@
         <v>24.3</v>
       </c>
       <c r="AA17" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="AB17" t="n">
-        <v>99.09999999999999</v>
+        <v>99</v>
       </c>
       <c r="AC17" t="n">
-        <v>-1.3</v>
+        <v>-1.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="AE17" t="n">
         <v>20</v>
       </c>
       <c r="AF17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AH17" t="n">
         <v>21</v>
       </c>
       <c r="AI17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AJ17" t="n">
         <v>8</v>
@@ -3499,31 +3566,31 @@
         <v>20</v>
       </c>
       <c r="AN17" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AO17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AP17" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AQ17" t="n">
         <v>11</v>
       </c>
       <c r="AR17" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AS17" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AT17" t="n">
         <v>20</v>
       </c>
       <c r="AU17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AW17" t="n">
         <v>11</v>
@@ -3532,7 +3599,7 @@
         <v>29</v>
       </c>
       <c r="AY17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ17" t="n">
         <v>30</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>4-10-2008-09</t>
+          <t>2009-04-10</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-4.8</v>
       </c>
       <c r="AD18" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AE18" t="n">
         <v>25</v>
@@ -3663,22 +3730,22 @@
         <v>25</v>
       </c>
       <c r="AH18" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AI18" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AJ18" t="n">
         <v>7</v>
       </c>
       <c r="AK18" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AL18" t="n">
         <v>19</v>
       </c>
       <c r="AM18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AN18" t="n">
         <v>24</v>
@@ -3690,7 +3757,7 @@
         <v>18</v>
       </c>
       <c r="AQ18" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AR18" t="n">
         <v>6</v>
@@ -3705,7 +3772,7 @@
         <v>17</v>
       </c>
       <c r="AV18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AW18" t="n">
         <v>28</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>4-10-2008-09</t>
+          <t>2009-04-10</t>
         </is>
       </c>
     </row>
@@ -3755,16 +3822,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E19" t="n">
         <v>32</v>
       </c>
       <c r="F19" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G19" t="n">
-        <v>0.405</v>
+        <v>0.41</v>
       </c>
       <c r="H19" t="n">
         <v>48.4</v>
@@ -3773,10 +3840,10 @@
         <v>35.8</v>
       </c>
       <c r="J19" t="n">
-        <v>79.8</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>0.449</v>
+        <v>0.448</v>
       </c>
       <c r="L19" t="n">
         <v>7.9</v>
@@ -3788,13 +3855,13 @@
         <v>0.374</v>
       </c>
       <c r="O19" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="P19" t="n">
         <v>24.3</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.777</v>
+        <v>0.778</v>
       </c>
       <c r="R19" t="n">
         <v>10.3</v>
@@ -3803,13 +3870,13 @@
         <v>29.5</v>
       </c>
       <c r="T19" t="n">
-        <v>39.7</v>
+        <v>39.9</v>
       </c>
       <c r="U19" t="n">
         <v>20</v>
       </c>
       <c r="V19" t="n">
-        <v>12.9</v>
+        <v>13.1</v>
       </c>
       <c r="W19" t="n">
         <v>6.9</v>
@@ -3827,25 +3894,25 @@
         <v>20.6</v>
       </c>
       <c r="AB19" t="n">
-        <v>98.40000000000001</v>
+        <v>98.5</v>
       </c>
       <c r="AC19" t="n">
         <v>-2.3</v>
       </c>
       <c r="AD19" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE19" t="n">
         <v>20</v>
       </c>
       <c r="AF19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AI19" t="n">
         <v>26</v>
@@ -3854,22 +3921,22 @@
         <v>18</v>
       </c>
       <c r="AK19" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AM19" t="n">
         <v>3</v>
       </c>
       <c r="AN19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AO19" t="n">
         <v>14</v>
       </c>
       <c r="AP19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AQ19" t="n">
         <v>12</v>
@@ -3881,7 +3948,7 @@
         <v>20</v>
       </c>
       <c r="AT19" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AU19" t="n">
         <v>26</v>
@@ -3890,19 +3957,19 @@
         <v>9</v>
       </c>
       <c r="AW19" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AX19" t="n">
         <v>17</v>
       </c>
       <c r="AY19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ19" t="n">
         <v>25</v>
       </c>
       <c r="BA19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BB19" t="n">
         <v>18</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>4-10-2008-09</t>
+          <t>2009-04-10</t>
         </is>
       </c>
     </row>
@@ -3937,16 +4004,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E20" t="n">
         <v>48</v>
       </c>
       <c r="F20" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G20" t="n">
-        <v>0.608</v>
+        <v>0.615</v>
       </c>
       <c r="H20" t="n">
         <v>48.1</v>
@@ -3955,10 +4022,10 @@
         <v>35.5</v>
       </c>
       <c r="J20" t="n">
-        <v>77.59999999999999</v>
+        <v>77.7</v>
       </c>
       <c r="K20" t="n">
-        <v>0.457</v>
+        <v>0.458</v>
       </c>
       <c r="L20" t="n">
         <v>6.8</v>
@@ -3970,13 +4037,13 @@
         <v>0.365</v>
       </c>
       <c r="O20" t="n">
-        <v>18.3</v>
+        <v>18.2</v>
       </c>
       <c r="P20" t="n">
         <v>22.6</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="R20" t="n">
         <v>9.9</v>
@@ -3988,19 +4055,19 @@
         <v>39.9</v>
       </c>
       <c r="U20" t="n">
-        <v>19.6</v>
+        <v>19.8</v>
       </c>
       <c r="V20" t="n">
-        <v>12.6</v>
+        <v>12.7</v>
       </c>
       <c r="W20" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="X20" t="n">
         <v>4.2</v>
       </c>
       <c r="Y20" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Z20" t="n">
         <v>20.4</v>
@@ -4012,10 +4079,10 @@
         <v>96.09999999999999</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AD20" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE20" t="n">
         <v>9</v>
@@ -4042,16 +4109,16 @@
         <v>13</v>
       </c>
       <c r="AM20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AN20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AO20" t="n">
         <v>23</v>
       </c>
       <c r="AP20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AQ20" t="n">
         <v>3</v>
@@ -4063,16 +4130,16 @@
         <v>16</v>
       </c>
       <c r="AT20" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AU20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AV20" t="n">
         <v>5</v>
       </c>
       <c r="AW20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AX20" t="n">
         <v>26</v>
@@ -4084,13 +4151,13 @@
         <v>11</v>
       </c>
       <c r="BA20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BB20" t="n">
         <v>25</v>
       </c>
       <c r="BC20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>4-10-2008-09</t>
+          <t>2009-04-10</t>
         </is>
       </c>
     </row>
@@ -4119,16 +4186,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E21" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F21" t="n">
         <v>49</v>
       </c>
       <c r="G21" t="n">
-        <v>0.388</v>
+        <v>0.38</v>
       </c>
       <c r="H21" t="n">
         <v>48.3</v>
@@ -4137,7 +4204,7 @@
         <v>38.5</v>
       </c>
       <c r="J21" t="n">
-        <v>86.5</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="K21" t="n">
         <v>0.445</v>
@@ -4146,7 +4213,7 @@
         <v>10.1</v>
       </c>
       <c r="M21" t="n">
-        <v>27.9</v>
+        <v>28</v>
       </c>
       <c r="N21" t="n">
         <v>0.362</v>
@@ -4161,16 +4228,16 @@
         <v>0.784</v>
       </c>
       <c r="R21" t="n">
-        <v>11.1</v>
+        <v>11</v>
       </c>
       <c r="S21" t="n">
-        <v>31.1</v>
+        <v>31</v>
       </c>
       <c r="T21" t="n">
-        <v>42.2</v>
+        <v>42.1</v>
       </c>
       <c r="U21" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="V21" t="n">
         <v>14.5</v>
@@ -4194,22 +4261,22 @@
         <v>105.3</v>
       </c>
       <c r="AC21" t="n">
-        <v>-2.8</v>
+        <v>-3</v>
       </c>
       <c r="AD21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE21" t="n">
         <v>22</v>
       </c>
       <c r="AF21" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG21" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AH21" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI21" t="n">
         <v>5</v>
@@ -4227,10 +4294,10 @@
         <v>1</v>
       </c>
       <c r="AN21" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AO21" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AP21" t="n">
         <v>22</v>
@@ -4245,16 +4312,16 @@
         <v>9</v>
       </c>
       <c r="AT21" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AU21" t="n">
+        <v>12</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>19</v>
+      </c>
+      <c r="AW21" t="n">
         <v>11</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>18</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>12</v>
       </c>
       <c r="AX21" t="n">
         <v>30</v>
@@ -4263,7 +4330,7 @@
         <v>22</v>
       </c>
       <c r="AZ21" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BA21" t="n">
         <v>29</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>4-10-2008-09</t>
+          <t>2009-04-10</t>
         </is>
       </c>
     </row>
@@ -4301,16 +4368,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E22" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F22" t="n">
         <v>57</v>
       </c>
       <c r="G22" t="n">
-        <v>0.278</v>
+        <v>0.269</v>
       </c>
       <c r="H22" t="n">
         <v>48.3</v>
@@ -4328,34 +4395,34 @@
         <v>4</v>
       </c>
       <c r="M22" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="N22" t="n">
-        <v>0.346</v>
+        <v>0.349</v>
       </c>
       <c r="O22" t="n">
-        <v>19.8</v>
+        <v>20</v>
       </c>
       <c r="P22" t="n">
-        <v>25.3</v>
+        <v>25.4</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.785</v>
+        <v>0.786</v>
       </c>
       <c r="R22" t="n">
         <v>12.2</v>
       </c>
       <c r="S22" t="n">
-        <v>30.4</v>
+        <v>30.3</v>
       </c>
       <c r="T22" t="n">
-        <v>42.6</v>
+        <v>42.5</v>
       </c>
       <c r="U22" t="n">
         <v>20.1</v>
       </c>
       <c r="V22" t="n">
-        <v>16.3</v>
+        <v>16.2</v>
       </c>
       <c r="W22" t="n">
         <v>7.3</v>
@@ -4364,7 +4431,7 @@
         <v>4.5</v>
       </c>
       <c r="Y22" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Z22" t="n">
         <v>20.3</v>
@@ -4373,13 +4440,13 @@
         <v>20.3</v>
       </c>
       <c r="AB22" t="n">
-        <v>96.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AC22" t="n">
-        <v>-6.3</v>
+        <v>-6.4</v>
       </c>
       <c r="AD22" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE22" t="n">
         <v>27</v>
@@ -4412,10 +4479,10 @@
         <v>28</v>
       </c>
       <c r="AO22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AP22" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AQ22" t="n">
         <v>9</v>
@@ -4424,22 +4491,22 @@
         <v>4</v>
       </c>
       <c r="AS22" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AT22" t="n">
         <v>6</v>
       </c>
       <c r="AU22" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AV22" t="n">
         <v>30</v>
       </c>
       <c r="AW22" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AX22" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AY22" t="n">
         <v>17</v>
@@ -4451,7 +4518,7 @@
         <v>20</v>
       </c>
       <c r="BB22" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BC22" t="n">
         <v>27</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>4-10-2008-09</t>
+          <t>2009-04-10</t>
         </is>
       </c>
     </row>
@@ -4483,16 +4550,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E23" t="n">
         <v>58</v>
       </c>
       <c r="F23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G23" t="n">
-        <v>0.734</v>
+        <v>0.744</v>
       </c>
       <c r="H23" t="n">
         <v>48.1</v>
@@ -4513,10 +4580,10 @@
         <v>26.4</v>
       </c>
       <c r="N23" t="n">
-        <v>0.382</v>
+        <v>0.384</v>
       </c>
       <c r="O23" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="P23" t="n">
         <v>27.5</v>
@@ -4525,7 +4592,7 @@
         <v>0.718</v>
       </c>
       <c r="R23" t="n">
-        <v>9.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="S23" t="n">
         <v>33.4</v>
@@ -4534,7 +4601,7 @@
         <v>43.2</v>
       </c>
       <c r="U23" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="V23" t="n">
         <v>14.1</v>
@@ -4558,10 +4625,10 @@
         <v>101.5</v>
       </c>
       <c r="AC23" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AD23" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE23" t="n">
         <v>4</v>
@@ -4576,13 +4643,13 @@
         <v>25</v>
       </c>
       <c r="AI23" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AJ23" t="n">
         <v>26</v>
       </c>
       <c r="AK23" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AL23" t="n">
         <v>1</v>
@@ -4591,10 +4658,10 @@
         <v>2</v>
       </c>
       <c r="AN23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AO23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AP23" t="n">
         <v>4</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>4-10-2008-09</t>
+          <t>2009-04-10</t>
         </is>
       </c>
     </row>
@@ -4665,25 +4732,25 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E24" t="n">
         <v>40</v>
       </c>
       <c r="F24" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G24" t="n">
-        <v>0.506</v>
+        <v>0.513</v>
       </c>
       <c r="H24" t="n">
         <v>48.1</v>
       </c>
       <c r="I24" t="n">
-        <v>36.5</v>
+        <v>36.6</v>
       </c>
       <c r="J24" t="n">
-        <v>79.7</v>
+        <v>79.8</v>
       </c>
       <c r="K24" t="n">
         <v>0.459</v>
@@ -4695,13 +4762,13 @@
         <v>13.1</v>
       </c>
       <c r="N24" t="n">
-        <v>0.318</v>
+        <v>0.319</v>
       </c>
       <c r="O24" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="P24" t="n">
-        <v>26.8</v>
+        <v>26.7</v>
       </c>
       <c r="Q24" t="n">
         <v>0.743</v>
@@ -4710,19 +4777,19 @@
         <v>12.6</v>
       </c>
       <c r="S24" t="n">
-        <v>28.6</v>
+        <v>28.7</v>
       </c>
       <c r="T24" t="n">
-        <v>41.2</v>
+        <v>41.3</v>
       </c>
       <c r="U24" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="V24" t="n">
         <v>14.1</v>
       </c>
       <c r="W24" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="X24" t="n">
         <v>5.1</v>
@@ -4737,13 +4804,13 @@
         <v>21.6</v>
       </c>
       <c r="AB24" t="n">
-        <v>97.09999999999999</v>
+        <v>97.2</v>
       </c>
       <c r="AC24" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="AD24" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE24" t="n">
         <v>15</v>
@@ -4776,7 +4843,7 @@
         <v>30</v>
       </c>
       <c r="AO24" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AP24" t="n">
         <v>6</v>
@@ -4794,10 +4861,10 @@
         <v>17</v>
       </c>
       <c r="AU24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AV24" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AW24" t="n">
         <v>5</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>4-10-2008-09</t>
+          <t>2009-04-10</t>
         </is>
       </c>
     </row>
@@ -4847,22 +4914,22 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E25" t="n">
         <v>43</v>
       </c>
       <c r="F25" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G25" t="n">
-        <v>0.544</v>
+        <v>0.551</v>
       </c>
       <c r="H25" t="n">
         <v>48.2</v>
       </c>
       <c r="I25" t="n">
-        <v>41.1</v>
+        <v>41.2</v>
       </c>
       <c r="J25" t="n">
         <v>81.5</v>
@@ -4871,31 +4938,31 @@
         <v>0.505</v>
       </c>
       <c r="L25" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="M25" t="n">
-        <v>17.7</v>
+        <v>17.8</v>
       </c>
       <c r="N25" t="n">
-        <v>0.382</v>
+        <v>0.383</v>
       </c>
       <c r="O25" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="P25" t="n">
-        <v>27.1</v>
+        <v>27.2</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.745</v>
+        <v>0.747</v>
       </c>
       <c r="R25" t="n">
         <v>10.8</v>
       </c>
       <c r="S25" t="n">
-        <v>30.8</v>
+        <v>30.9</v>
       </c>
       <c r="T25" t="n">
-        <v>41.6</v>
+        <v>41.7</v>
       </c>
       <c r="U25" t="n">
         <v>23.2</v>
@@ -4910,22 +4977,22 @@
         <v>5.1</v>
       </c>
       <c r="Y25" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Z25" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="AA25" t="n">
         <v>22.8</v>
       </c>
       <c r="AB25" t="n">
-        <v>109.2</v>
+        <v>109.5</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="AD25" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE25" t="n">
         <v>13</v>
@@ -4937,25 +5004,25 @@
         <v>13</v>
       </c>
       <c r="AH25" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI25" t="n">
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AK25" t="n">
         <v>1</v>
       </c>
       <c r="AL25" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AM25" t="n">
         <v>19</v>
       </c>
       <c r="AN25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AO25" t="n">
         <v>5</v>
@@ -4979,13 +5046,13 @@
         <v>2</v>
       </c>
       <c r="AV25" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AW25" t="n">
         <v>18</v>
       </c>
       <c r="AX25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY25" t="n">
         <v>10</v>
@@ -5000,7 +5067,7 @@
         <v>1</v>
       </c>
       <c r="BC25" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BD25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>4-10-2008-09</t>
+          <t>2009-04-10</t>
         </is>
       </c>
     </row>
@@ -5032,13 +5099,13 @@
         <v>78</v>
       </c>
       <c r="E26" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F26" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G26" t="n">
-        <v>0.654</v>
+        <v>0.641</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
@@ -5050,7 +5117,7 @@
         <v>79.2</v>
       </c>
       <c r="K26" t="n">
-        <v>0.465</v>
+        <v>0.464</v>
       </c>
       <c r="L26" t="n">
         <v>7.2</v>
@@ -5059,13 +5126,13 @@
         <v>18.9</v>
       </c>
       <c r="N26" t="n">
-        <v>0.381</v>
+        <v>0.382</v>
       </c>
       <c r="O26" t="n">
-        <v>18.8</v>
+        <v>18.5</v>
       </c>
       <c r="P26" t="n">
-        <v>24.5</v>
+        <v>24.2</v>
       </c>
       <c r="Q26" t="n">
         <v>0.767</v>
@@ -5083,7 +5150,7 @@
         <v>20.3</v>
       </c>
       <c r="V26" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="W26" t="n">
         <v>6.7</v>
@@ -5092,31 +5159,31 @@
         <v>4.9</v>
       </c>
       <c r="Y26" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="Z26" t="n">
         <v>20.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>21.3</v>
+        <v>21.1</v>
       </c>
       <c r="AB26" t="n">
-        <v>99.7</v>
+        <v>99.3</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="AD26" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="AE26" t="n">
         <v>7</v>
       </c>
       <c r="AF26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH26" t="n">
         <v>11</v>
@@ -5140,13 +5207,13 @@
         <v>7</v>
       </c>
       <c r="AO26" t="n">
+        <v>19</v>
+      </c>
+      <c r="AP26" t="n">
         <v>17</v>
       </c>
-      <c r="AP26" t="n">
-        <v>15</v>
-      </c>
       <c r="AQ26" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AR26" t="n">
         <v>1</v>
@@ -5158,7 +5225,7 @@
         <v>15</v>
       </c>
       <c r="AU26" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AV26" t="n">
         <v>7</v>
@@ -5173,10 +5240,10 @@
         <v>3</v>
       </c>
       <c r="AZ26" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BB26" t="n">
         <v>14</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>4-10-2008-09</t>
+          <t>2009-04-10</t>
         </is>
       </c>
     </row>
@@ -5211,85 +5278,85 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E27" t="n">
         <v>16</v>
       </c>
       <c r="F27" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G27" t="n">
-        <v>0.203</v>
+        <v>0.205</v>
       </c>
       <c r="H27" t="n">
         <v>48.6</v>
       </c>
       <c r="I27" t="n">
-        <v>36.5</v>
+        <v>36.6</v>
       </c>
       <c r="J27" t="n">
-        <v>81.59999999999999</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="K27" t="n">
-        <v>0.447</v>
+        <v>0.449</v>
       </c>
       <c r="L27" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="M27" t="n">
         <v>19.4</v>
       </c>
       <c r="N27" t="n">
-        <v>0.366</v>
+        <v>0.368</v>
       </c>
       <c r="O27" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="P27" t="n">
-        <v>25.9</v>
+        <v>26</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.799</v>
+        <v>0.801</v>
       </c>
       <c r="R27" t="n">
-        <v>10.3</v>
+        <v>10.1</v>
       </c>
       <c r="S27" t="n">
         <v>28.8</v>
       </c>
       <c r="T27" t="n">
-        <v>39</v>
+        <v>38.9</v>
       </c>
       <c r="U27" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="V27" t="n">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="W27" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="X27" t="n">
         <v>4.2</v>
       </c>
       <c r="Y27" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="Z27" t="n">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="AA27" t="n">
         <v>21.3</v>
       </c>
       <c r="AB27" t="n">
-        <v>100.8</v>
+        <v>101.1</v>
       </c>
       <c r="AC27" t="n">
-        <v>-8.9</v>
+        <v>-8.6</v>
       </c>
       <c r="AD27" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE27" t="n">
         <v>30</v>
@@ -5304,13 +5371,13 @@
         <v>4</v>
       </c>
       <c r="AI27" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AJ27" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AK27" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AL27" t="n">
         <v>10</v>
@@ -5319,7 +5386,7 @@
         <v>11</v>
       </c>
       <c r="AN27" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO27" t="n">
         <v>4</v>
@@ -5334,13 +5401,13 @@
         <v>25</v>
       </c>
       <c r="AS27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AT27" t="n">
         <v>29</v>
       </c>
       <c r="AU27" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AV27" t="n">
         <v>26</v>
@@ -5358,13 +5425,13 @@
         <v>29</v>
       </c>
       <c r="BA27" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BB27" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BC27" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BD27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>4-10-2008-09</t>
+          <t>2009-04-10</t>
         </is>
       </c>
     </row>
@@ -5393,16 +5460,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E28" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F28" t="n">
         <v>28</v>
       </c>
       <c r="G28" t="n">
-        <v>0.646</v>
+        <v>0.641</v>
       </c>
       <c r="H28" t="n">
         <v>48.5</v>
@@ -5411,7 +5478,7 @@
         <v>37.1</v>
       </c>
       <c r="J28" t="n">
-        <v>79.5</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="K28" t="n">
         <v>0.466</v>
@@ -5423,28 +5490,28 @@
         <v>19.7</v>
       </c>
       <c r="N28" t="n">
-        <v>0.387</v>
+        <v>0.386</v>
       </c>
       <c r="O28" t="n">
-        <v>15.2</v>
+        <v>15</v>
       </c>
       <c r="P28" t="n">
-        <v>19.8</v>
+        <v>19.6</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.765</v>
+        <v>0.767</v>
       </c>
       <c r="R28" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="S28" t="n">
         <v>32</v>
       </c>
       <c r="T28" t="n">
-        <v>40.7</v>
+        <v>40.8</v>
       </c>
       <c r="U28" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="V28" t="n">
         <v>11.7</v>
@@ -5459,34 +5526,34 @@
         <v>4.3</v>
       </c>
       <c r="Z28" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="AA28" t="n">
-        <v>18.4</v>
+        <v>18.3</v>
       </c>
       <c r="AB28" t="n">
-        <v>96.90000000000001</v>
+        <v>96.8</v>
       </c>
       <c r="AC28" t="n">
         <v>3.4</v>
       </c>
       <c r="AD28" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE28" t="n">
         <v>7</v>
       </c>
       <c r="AF28" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG28" t="n">
         <v>7</v>
       </c>
-      <c r="AG28" t="n">
-        <v>8</v>
-      </c>
       <c r="AH28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI28" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AJ28" t="n">
         <v>21</v>
@@ -5522,7 +5589,7 @@
         <v>19</v>
       </c>
       <c r="AU28" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AV28" t="n">
         <v>1</v>
@@ -5543,7 +5610,7 @@
         <v>30</v>
       </c>
       <c r="BB28" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BC28" t="n">
         <v>8</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>4-10-2008-09</t>
+          <t>2009-04-10</t>
         </is>
       </c>
     </row>
@@ -5575,16 +5642,16 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E29" t="n">
         <v>30</v>
       </c>
       <c r="F29" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G29" t="n">
-        <v>0.38</v>
+        <v>0.385</v>
       </c>
       <c r="H29" t="n">
         <v>48.3</v>
@@ -5593,28 +5660,28 @@
         <v>37.1</v>
       </c>
       <c r="J29" t="n">
-        <v>81.09999999999999</v>
+        <v>81</v>
       </c>
       <c r="K29" t="n">
-        <v>0.457</v>
+        <v>0.458</v>
       </c>
       <c r="L29" t="n">
         <v>5.9</v>
       </c>
       <c r="M29" t="n">
-        <v>15.8</v>
+        <v>15.7</v>
       </c>
       <c r="N29" t="n">
         <v>0.374</v>
       </c>
       <c r="O29" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="P29" t="n">
         <v>22.7</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.825</v>
+        <v>0.826</v>
       </c>
       <c r="R29" t="n">
         <v>9.5</v>
@@ -5638,13 +5705,13 @@
         <v>4.7</v>
       </c>
       <c r="Y29" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Z29" t="n">
         <v>19.3</v>
       </c>
       <c r="AA29" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="AB29" t="n">
         <v>98.8</v>
@@ -5653,25 +5720,25 @@
         <v>-3.2</v>
       </c>
       <c r="AD29" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF29" t="n">
         <v>22</v>
       </c>
       <c r="AG29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AH29" t="n">
         <v>14</v>
       </c>
       <c r="AI29" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AJ29" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AK29" t="n">
         <v>15</v>
@@ -5683,13 +5750,13 @@
         <v>23</v>
       </c>
       <c r="AN29" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AO29" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AP29" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AQ29" t="n">
         <v>1</v>
@@ -5716,7 +5783,7 @@
         <v>16</v>
       </c>
       <c r="AY29" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ29" t="n">
         <v>3</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>4-10-2008-09</t>
+          <t>2009-04-10</t>
         </is>
       </c>
     </row>
@@ -5757,16 +5824,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E30" t="n">
         <v>47</v>
       </c>
       <c r="F30" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G30" t="n">
-        <v>0.595</v>
+        <v>0.603</v>
       </c>
       <c r="H30" t="n">
         <v>48.5</v>
@@ -5778,7 +5845,7 @@
         <v>80.8</v>
       </c>
       <c r="K30" t="n">
-        <v>0.475</v>
+        <v>0.476</v>
       </c>
       <c r="L30" t="n">
         <v>4.8</v>
@@ -5796,7 +5863,7 @@
         <v>28.2</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.771</v>
+        <v>0.77</v>
       </c>
       <c r="R30" t="n">
         <v>11.4</v>
@@ -5817,7 +5884,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="X30" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Y30" t="n">
         <v>5.1</v>
@@ -5832,22 +5899,22 @@
         <v>103.4</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="AD30" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE30" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AF30" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG30" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI30" t="n">
         <v>6</v>
@@ -5859,7 +5926,7 @@
         <v>3</v>
       </c>
       <c r="AL30" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AM30" t="n">
         <v>26</v>
@@ -5895,10 +5962,10 @@
         <v>1</v>
       </c>
       <c r="AX30" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY30" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AZ30" t="n">
         <v>23</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>4-10-2008-09</t>
+          <t>2009-04-10</t>
         </is>
       </c>
     </row>
@@ -5939,52 +6006,52 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F31" t="n">
         <v>61</v>
       </c>
       <c r="G31" t="n">
-        <v>0.238</v>
+        <v>0.228</v>
       </c>
       <c r="H31" t="n">
         <v>48.1</v>
       </c>
       <c r="I31" t="n">
-        <v>36.5</v>
+        <v>36.4</v>
       </c>
       <c r="J31" t="n">
         <v>81.2</v>
       </c>
       <c r="K31" t="n">
-        <v>0.449</v>
+        <v>0.448</v>
       </c>
       <c r="L31" t="n">
         <v>4.8</v>
       </c>
       <c r="M31" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="N31" t="n">
         <v>0.331</v>
       </c>
       <c r="O31" t="n">
-        <v>18.1</v>
+        <v>18.2</v>
       </c>
       <c r="P31" t="n">
         <v>23.7</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.766</v>
+        <v>0.767</v>
       </c>
       <c r="R31" t="n">
         <v>11.7</v>
       </c>
       <c r="S31" t="n">
-        <v>28.4</v>
+        <v>28.3</v>
       </c>
       <c r="T31" t="n">
         <v>40</v>
@@ -5999,7 +6066,7 @@
         <v>7.5</v>
       </c>
       <c r="X31" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Y31" t="n">
         <v>5.3</v>
@@ -6014,10 +6081,10 @@
         <v>95.90000000000001</v>
       </c>
       <c r="AC31" t="n">
-        <v>-7.5</v>
+        <v>-7.7</v>
       </c>
       <c r="AD31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE31" t="n">
         <v>28</v>
@@ -6032,16 +6099,16 @@
         <v>29</v>
       </c>
       <c r="AI31" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AJ31" t="n">
         <v>13</v>
       </c>
       <c r="AK31" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL31" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AM31" t="n">
         <v>25</v>
@@ -6050,13 +6117,13 @@
         <v>29</v>
       </c>
       <c r="AO31" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP31" t="n">
         <v>20</v>
       </c>
       <c r="AQ31" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AR31" t="n">
         <v>8</v>
@@ -6068,22 +6135,22 @@
         <v>23</v>
       </c>
       <c r="AU31" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AV31" t="n">
         <v>12</v>
       </c>
       <c r="AW31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX31" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AY31" t="n">
         <v>23</v>
       </c>
       <c r="AZ31" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BA31" t="n">
         <v>26</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>4-10-2008-09</t>
+          <t>2009-04-10</t>
         </is>
       </c>
     </row>
